--- a/data/trans_orig/P44D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>51986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62948</t>
+          <t>62889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98175</t>
+          <t>98526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110415</t>
+          <t>110451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45216</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>27326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51279</t>
+          <t>52935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69975</t>
+          <t>70025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>30289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>49239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>86832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105198</t>
+          <t>104747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77949</t>
+          <t>77615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96252</t>
+          <t>96195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172818</t>
+          <t>171371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196920</t>
+          <t>197482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2016 (tasa de respuesta: 93,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>47145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53183</t>
+          <t>53167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>104577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57166</t>
+          <t>57201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69508</t>
+          <t>69862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24227</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30988</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85731</t>
+          <t>85203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99338</t>
+          <t>99331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>33788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32432</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46239</t>
+          <t>45783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124180</t>
+          <t>123618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141595</t>
+          <t>141752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88813</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101961</t>
+          <t>101908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217752</t>
+          <t>218208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239828</t>
+          <t>239833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132923</t>
+          <t>132958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140192</t>
+          <t>140141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166120</t>
+          <t>166322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170132</t>
+          <t>170274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301521</t>
+          <t>301231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>309346</t>
+          <t>309364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>46037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60122</t>
+          <t>59003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461768</t>
+          <t>465649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505632</t>
+          <t>506256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201167</t>
+          <t>201617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212754</t>
+          <t>212721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674579</t>
+          <t>675698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721626</t>
+          <t>721173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18915</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>34451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>24026</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34318</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54011</t>
+          <t>54404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89857</t>
+          <t>89454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104990</t>
+          <t>105506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61591</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72984</t>
+          <t>72777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155621</t>
+          <t>155228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175314</t>
+          <t>175056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81727</t>
+          <t>82021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49637</t>
+          <t>44711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114694</t>
+          <t>113486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>695525</t>
+          <t>695231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>755779</t>
+          <t>755246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435534</t>
+          <t>435406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>451549</t>
+          <t>451964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1141982</t>
+          <t>1143190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1207039</t>
+          <t>1211965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>43591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51986</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>62915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98526</t>
+          <t>99440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110451</t>
+          <t>110566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>32185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>45281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>27292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>52650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70025</t>
+          <t>70400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>16826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21946</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30289</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49239</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104747</t>
+          <t>105288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77615</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96195</t>
+          <t>96200</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171371</t>
+          <t>173689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>197482</t>
+          <t>198251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>47217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53167</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104577</t>
+          <t>104894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>22316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57201</t>
+          <t>57598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>23400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>30944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85203</t>
+          <t>84487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99331</t>
+          <t>98991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>25430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,08%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32994</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45783</t>
+          <t>47618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123618</t>
+          <t>124168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141752</t>
+          <t>141604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>88603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101908</t>
+          <t>101910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218208</t>
+          <t>216373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239833</t>
+          <t>239741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>137288</t>
+          <t>146511</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132958</t>
+          <t>141533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140141</t>
+          <t>149349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>168955</t>
+          <t>186183</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166322</t>
+          <t>183678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170274</t>
+          <t>187634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>306242</t>
+          <t>332696</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301231</t>
+          <t>327303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>309364</t>
+          <t>335973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>141662</t>
+          <t>151006</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141662</t>
+          <t>151006</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141662</t>
+          <t>151006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>170682</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170682</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170682</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>312343</t>
+          <t>339074</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>312343</t>
+          <t>339074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>312343</t>
+          <t>339074</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46037</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>23267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59003</t>
+          <t>52861</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>489732</t>
+          <t>266438</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465649</t>
+          <t>256473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506256</t>
+          <t>274248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>207755</t>
+          <t>228121</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>221548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212721</t>
+          <t>233460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>697487</t>
+          <t>494559</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675698</t>
+          <t>482780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721173</t>
+          <t>504060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>511686</t>
+          <t>290826</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511686</t>
+          <t>290826</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511686</t>
+          <t>290826</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>223015</t>
+          <t>244815</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>223015</t>
+          <t>244815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>223015</t>
+          <t>244815</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>734701</t>
+          <t>535641</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>734701</t>
+          <t>535641</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>734701</t>
+          <t>535641</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25605</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34451</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18294</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>14532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>37919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54404</t>
+          <t>59411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>98300</t>
+          <t>102613</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>93821</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105506</t>
+          <t>110950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67433</t>
+          <t>77191</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61701</t>
+          <t>69928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72777</t>
+          <t>82588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>165733</t>
+          <t>179804</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155228</t>
+          <t>167812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175056</t>
+          <t>189304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123905</t>
+          <t>130103</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123905</t>
+          <t>130103</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123905</t>
+          <t>130103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>209632</t>
+          <t>227223</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209632</t>
+          <t>227223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>209632</t>
+          <t>227223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>42751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>70709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>80323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113486</t>
+          <t>112123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>725319</t>
+          <t>515562</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>695231</t>
+          <t>501226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>755246</t>
+          <t>529184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>444142</t>
+          <t>491496</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435406</t>
+          <t>480907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>451964</t>
+          <t>499392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1169462</t>
+          <t>1007058</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1143190</t>
+          <t>989814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211965</t>
+          <t>1021614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>777252</t>
+          <t>571935</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>777252</t>
+          <t>571935</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>777252</t>
+          <t>571935</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1256676</t>
+          <t>1101937</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1256676</t>
+          <t>1101937</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1256676</t>
+          <t>1101937</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
